--- a/TASK2/Scenariji/SC12_PregledHistorijeDolazaka.xlsx
+++ b/TASK2/Scenariji/SC12_PregledHistorijeDolazaka.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clan pregledava svoju historiju dolazaka u teretanu.</t>
+          <t>Član pregledava svoju historiju dolazaka u teretanu.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Evidentiranje svakog dolaska clana sa tacnim vremenom</t>
+          <t>Evidentiranje svakog dolaska člana sa tačnim vremenom</t>
         </is>
       </c>
     </row>
@@ -497,26 +497,26 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Clan je prijavljen na sistem.</t>
+          <t>Član je prijavljen na sistem.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Clan ima uvid u svoju historiju dolazaka.</t>
+          <t>Član ima uvid u svoju historiju dolazaka.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Clan otvara profil, bira opciju za pregled dolazaka, sistem prikazuje historiju.</t>
+          <t>Član otvara profil, bira opciju za pregled dolazaka, sistem prikazuje historiju.</t>
         </is>
       </c>
     </row>
@@ -573,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -583,7 +584,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -609,7 +610,7 @@
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>3. Dohvatanje svih evidentiranih dolazaka clana</t>
+          <t>3. Dohvaćanje svih evidentiranih dolazaka člana</t>
         </is>
       </c>
     </row>
@@ -627,6 +628,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
@@ -637,7 +639,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
